--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="VENTA MENSUAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VENTAS POR GRUPO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,7 +58,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -65,6 +66,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,4 +531,272 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>240X120 PORCELANATO</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>240X80 PORCELANATO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FREGADEROS DE COCINA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GRANITO</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GRIFERIAS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>INODOROS</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LAVABOS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PANELES DECORATIVOS</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PIEDRA SINTERIZADA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>PUERTAS DE SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SAL SOLUBLE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>NO RESURTIBLES</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>PANELES PVC</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>PANELES PU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EDESA SA</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -435,11 +435,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -512,19 +512,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PYCCA S.A.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>107.16</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="3" t="n">
+        <v>107.16</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -539,11 +566,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -715,84 +742,144 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>0 de 1</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PYCCA S.A.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>0 de 2</t>
         </is>
       </c>
     </row>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="VENTA MENSUAL" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="VENTAS POR GRUPO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CUMPLIMIENTO MENSUAL" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -69,6 +70,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,4 +891,125 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>POR CUMPLIR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CUMPLIMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -440,11 +440,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -544,19 +544,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="3" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="3" t="n">
         <v>107.16</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>58.9</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="F5" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -571,11 +598,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -807,84 +834,144 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>0 de 2</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>1 de 3</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>0 de 3</t>
         </is>
       </c>
     </row>
@@ -907,7 +994,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -981,13 +1068,13 @@
         <v>15000</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15000</v>
+        <v>14920</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>0.005333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -1000,13 +1087,13 @@
         <v>15000</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15000</v>
+        <v>14920</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>0.005333333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -448,7 +448,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>80</v>
+        <v>720.05</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -581,7 +581,7 @@
         <v>58.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>80</v>
+        <v>720.05</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>80</v>
+        <v>720.05</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -992,9 +992,9 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1068,13 +1068,13 @@
         <v>15000</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>80</v>
+        <v>720.05</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14920</v>
+        <v>14279.95</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.005333333333333333</v>
+        <v>0.04800333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -1087,13 +1087,13 @@
         <v>15000</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>80</v>
+        <v>720.05</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14920</v>
+        <v>14279.95</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.005333333333333333</v>
+        <v>0.04800333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -445,10 +445,10 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -465,22 +465,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>107.16</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>58.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>58.9</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>720.05</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>720.05</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -572,16 +572,16 @@
     </row>
     <row r="5">
       <c r="C5" s="3" t="n">
-        <v>107.16</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>58.9</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>58.9</v>
+        <v>720.05</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>720.05</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>720.05</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>1 de 3</t>
+          <t>0 de 3</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -448,7 +448,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -510,7 +510,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -581,7 +581,7 @@
         <v>720.05</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 de 3</t>
+          <t>1 de 3</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -440,12 +440,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -497,20 +497,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>CONSTRUMERCADO S.A.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>1125.31</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>24.18</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -524,20 +524,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>58.9</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -551,39 +551,66 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PYCCA S.A.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>720.05</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="2" t="n">
+        <v>200.02</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="3" t="n">
+        <v>1125.31</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>83.08</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>720.05</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>503.56</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="F6" s="3" t="n">
+        <v>703.58</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -598,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -721,14 +748,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>CONSTRUMERCADO S.A.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -781,14 +808,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -841,137 +868,197 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PYCCA S.A.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1 de 3</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>0 de 3</t>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>200.02</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1 de 4</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>1 de 4</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>0 de 4</t>
         </is>
       </c>
     </row>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -1131,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>-503.56</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15000</v>
+        <v>13101</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>720.05</v>
+        <v>200.02</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14279.95</v>
+        <v>12900.98</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.04800333333333333</v>
+        <v>0.01526753682924968</v>
       </c>
     </row>
     <row r="4">
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15000</v>
+        <v>13101</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>720.05</v>
+        <v>703.58</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14279.95</v>
+        <v>12397.42</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.04800333333333333</v>
+        <v>0.05370429738187925</v>
       </c>
     </row>
   </sheetData>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -591,7 +591,7 @@
         <v>720.05</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>200.02</v>
+        <v>392.56</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>720.05</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>703.58</v>
+        <v>896.12</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>200.02</v>
+        <v>392.56</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>13101</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>200.02</v>
+        <v>392.56</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12900.98</v>
+        <v>12708.44</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.01526753682924968</v>
+        <v>0.02996412487596367</v>
       </c>
     </row>
     <row r="4">
@@ -1174,13 +1174,13 @@
         <v>13101</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>703.58</v>
+        <v>896.12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12397.42</v>
+        <v>12204.88</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.05370429738187925</v>
+        <v>0.06840088542859324</v>
       </c>
     </row>
   </sheetData>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -551,14 +551,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>MEGAMETALES S.A.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>58.9</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -578,39 +578,93 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>MOBILTROICORP S.A.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PYCCA S.A.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>720.05</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>392.56</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="3" t="n">
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="3" t="n">
         <v>1125.31</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>83.08</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>720.05</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>896.12</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -625,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -868,7 +922,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>MEGAMETALES S.A.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -928,137 +982,257 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>MOBILTROICORP S.A.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PYCCA S.A.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>392.56</v>
       </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1 de 4</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>1 de 4</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>0 de 4</t>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>1 de 6</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>1 de 6</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>0 de 6</t>
         </is>
       </c>
     </row>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -510,7 +510,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>320.79</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>720.05</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>896.12</v>
+        <v>1216.91</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>320.79</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>1 de 6</t>
+          <t>2 de 6</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1329,13 +1329,13 @@
         <v>13101</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>392.56</v>
+        <v>713.35</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12708.44</v>
+        <v>12387.65</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.02996412487596367</v>
+        <v>0.05445004198152813</v>
       </c>
     </row>
     <row r="4">
@@ -1348,13 +1348,13 @@
         <v>13101</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>896.12</v>
+        <v>1216.91</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12204.88</v>
+        <v>11884.09</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.06840088542859324</v>
+        <v>0.09288680253415771</v>
       </c>
     </row>
   </sheetData>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -440,12 +440,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -497,20 +497,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUMERCADO S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1125.31</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>24.18</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>320.79</v>
+        <v>503.56</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -524,7 +524,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>MEGAMETALES S.A.</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -551,7 +551,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEGAMETALES S.A.</t>
+          <t>MOBILTROICORP S.A.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -578,14 +578,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOBILTROICORP S.A.</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>58.9</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -605,66 +605,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>720.05</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>392.56</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>58.9</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>720.05</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>392.56</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="3" t="n">
-        <v>1125.31</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>83.08</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>720.05</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1216.91</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="F7" s="3" t="n">
+        <v>896.12</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -679,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -802,14 +775,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CONSTRUMERCADO S.A.</t>
+          <t>EDESA SA</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -836,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>320.79</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -862,14 +835,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>MEGAMETALES S.A.</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -922,7 +895,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEGAMETALES S.A.</t>
+          <t>MOBILTROICORP S.A.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -982,7 +955,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOBILTROICORP S.A.</t>
+          <t>PYCCA S.A.</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -1042,7 +1015,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PYCCA S.A.</t>
+          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -1076,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>392.56</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -1095,144 +1068,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>392.56</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>1 de 6</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>2 de 6</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>0 de 6</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1 de 5</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>1 de 5</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>0 de 5</t>
         </is>
       </c>
     </row>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -446,9 +446,9 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -465,22 +465,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -507,10 +507,10 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>58.9</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>58.9</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -612,13 +612,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>720.05</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>720.05</v>
+        <v>392.56</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>392.56</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
     </row>
     <row r="7">
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>58.9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>58.9</v>
+        <v>720.05</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>720.05</v>
+        <v>896.12</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>896.12</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>392.56</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1 de 5</t>
+          <t>0 de 5</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>1 de 5</t>
+          <t>0 de 5</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -440,14 +440,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>MOBILTROICORP S.A.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -507,7 +507,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -517,127 +517,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MEGAMETALES S.A.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MOBILTROICORP S.A.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PYCCA S.A.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>720.05</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>392.56</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>720.05</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>896.12</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -652,11 +544,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -775,7 +667,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDESA SA</t>
+          <t>MOBILTROICORP S.A.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -828,324 +720,84 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MEGAMETALES S.A.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MOBILTROICORP S.A.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PYCCA S.A.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TIENDAS INDUSTRIALES ASOCIADAS TIA S. A.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>0 de 5</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>0 de 1</t>
         </is>
       </c>
     </row>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -812,15 +812,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,56 +870,32 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>503.56</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-503.56</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CASTRO CALDERON VERONICA SOBEIDA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PORCELANATO</t>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13101</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>713.35</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12387.65</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05445004198152813</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>13101</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1216.91</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>11884.09</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.09288680253415771</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -445,10 +445,10 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -465,22 +465,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -445,10 +445,10 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -465,22 +465,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
